--- a/ONCHO/Impact Assessments/Nigeria/2025/river states ia/ng_oncho_stop_2507_2_part_ia_rs.xlsx
+++ b/ONCHO/Impact Assessments/Nigeria/2025/river states ia/ng_oncho_stop_2507_2_part_ia_rs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river states\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Impact Assessments\Nigeria\2025\river states ia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714E4B95-E26C-43F4-A411-DF6C19B49057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4CE6EFE-052C-4955-8E9D-B0666E306ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -268,12 +268,6 @@
     <t>${p_cluster_name}</t>
   </si>
   <si>
-    <t>. &gt;= 20</t>
-  </si>
-  <si>
-    <t>Age must be 20 or old</t>
-  </si>
-  <si>
     <t>How many years has the respondent lived in the area? (&lt;10 years end survey)</t>
   </si>
   <si>
@@ -283,12 +277,6 @@
     <t>p_travel_more_than_15_km</t>
   </si>
   <si>
-    <t>. &gt;= 10 and . &lt;= ${p_age_yrs}</t>
-  </si>
-  <si>
-    <t>The value must be 10 or more and not be greater than the age</t>
-  </si>
-  <si>
     <t xml:space="preserve">Does the respondent took IVM in past 12 months? </t>
   </si>
   <si>
@@ -325,9 +313,6 @@
     <t>Where he took IVM last past 12 months</t>
   </si>
   <si>
-    <t>ng_oncho_stop_2507_2_part_ia_rs</t>
-  </si>
-  <si>
     <t>calculate</t>
   </si>
   <si>
@@ -403,9 +388,6 @@
     <t>join(' ', ${p_code_id})</t>
   </si>
   <si>
-    <t>ng2507part</t>
-  </si>
-  <si>
     <t>C2</t>
   </si>
   <si>
@@ -427,7 +409,25 @@
     <t>This ID was alredy used</t>
   </si>
   <si>
-    <t>(River State 2025 July) - 2. Participant Form V2</t>
+    <t>. &gt;= 5 and . &lt;= 9</t>
+  </si>
+  <si>
+    <t>Age must be between 5 and 9</t>
+  </si>
+  <si>
+    <t>. &lt;= ${p_age_yrs}</t>
+  </si>
+  <si>
+    <t>The value must not be greater than the age</t>
+  </si>
+  <si>
+    <t>ng_oncho_stop_2507_2_part_ia_rs_v2</t>
+  </si>
+  <si>
+    <t>(River State 2025 July) - 2. Participant Form V2.1</t>
+  </si>
+  <si>
+    <t>ng2507part2</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1045,7 @@
         <v>13</v>
       </c>
       <c r="O1" s="31" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P1" s="32" t="s">
         <v>69</v>
@@ -1057,10 +1057,10 @@
         <v>71</v>
       </c>
       <c r="S1" s="32" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="T1" s="31" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:20" s="7" customFormat="1">
@@ -1219,10 +1219,10 @@
     </row>
     <row r="8" spans="1:20" s="35" customFormat="1">
       <c r="A8" s="33" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -1231,7 +1231,7 @@
       <c r="G8" s="34"/>
       <c r="H8" s="33"/>
       <c r="I8" s="34" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="J8" s="34"/>
       <c r="K8" s="34"/>
@@ -1249,13 +1249,13 @@
     </row>
     <row r="9" spans="1:20" s="1" customFormat="1">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="10" spans="1:20" s="35" customFormat="1">
       <c r="A10" s="33" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C10" s="34"/>
       <c r="D10" s="34"/>
@@ -1281,7 +1281,7 @@
       <c r="G10" s="34"/>
       <c r="H10" s="33"/>
       <c r="I10" s="34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J10" s="34"/>
       <c r="K10" s="34"/>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="11" spans="1:20" s="35" customFormat="1" ht="31.5">
       <c r="A11" s="33" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="C11" s="34"/>
       <c r="D11" s="34"/>
@@ -1311,7 +1311,7 @@
       <c r="G11" s="34"/>
       <c r="H11" s="33"/>
       <c r="I11" s="34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J11" s="34"/>
       <c r="K11" s="34"/>
@@ -1355,13 +1355,13 @@
     </row>
     <row r="13" spans="1:20" s="15" customFormat="1">
       <c r="A13" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="22"/>
@@ -1379,20 +1379,20 @@
     </row>
     <row r="14" spans="1:20" s="15" customFormat="1" ht="31.5">
       <c r="A14" s="22" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
       <c r="H14" s="22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I14" s="22"/>
       <c r="J14" s="22" t="s">
@@ -1406,17 +1406,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
       <c r="F15" s="25"/>
       <c r="G15" s="23"/>
       <c r="H15" s="24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23" t="s">
@@ -1433,21 +1433,21 @@
         <v>35</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H16" s="24" t="s">
         <v>34</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J16" s="24"/>
       <c r="K16" s="24"/>
@@ -1455,10 +1455,10 @@
         <v>20</v>
       </c>
       <c r="S16" s="8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T16" s="26" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:19" s="7" customFormat="1">
@@ -1514,10 +1514,10 @@
       </c>
       <c r="D19" s="8"/>
       <c r="F19" s="7" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>34</v>
@@ -1531,17 +1531,17 @@
         <v>14</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D20" s="8"/>
       <c r="F20" s="7" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>34</v>
@@ -1555,10 +1555,10 @@
         <v>31</v>
       </c>
       <c r="B21" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="D21" s="8"/>
       <c r="H21" s="8" t="s">
@@ -1573,10 +1573,10 @@
         <v>31</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D22" s="8"/>
       <c r="H22" s="8" t="s">
@@ -1588,17 +1588,17 @@
     </row>
     <row r="23" spans="1:19" s="7" customFormat="1" ht="31.5">
       <c r="A23" s="7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D23" s="8"/>
       <c r="H23" s="8" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>20</v>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="27" spans="1:19" s="16" customFormat="1">
       <c r="A27" s="29" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="20"/>
@@ -1803,7 +1803,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="27" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B6" s="27" t="s">
         <v>62</v>
@@ -1816,13 +1816,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="27" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="13"/>
@@ -1835,46 +1835,46 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>66</v>
